--- a/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260702.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260702.xlsx
@@ -865,17 +865,17 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>56,971,847</t>
+          <t>106,711,606</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -887,17 +887,17 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>106,711,606</t>
+          <t>56,971,847</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
@@ -1063,17 +1063,17 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>254,771,648</t>
+          <t>2,240,054</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -1085,17 +1085,17 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>2,240,054</t>
+          <t>254,771,648</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -1195,17 +1195,17 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>16,434,857</t>
+          <t>24,587,023</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -1217,17 +1217,17 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>24,587,023</t>
+          <t>16,434,857</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -1261,17 +1261,17 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>2883</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>凱基金</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>1,188,384</t>
+          <t>339,440,488</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -1283,17 +1283,17 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>2883</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>凱基金</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>339,440,488</t>
+          <t>1,188,384</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -1305,17 +1305,17 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>42,156,224</t>
+          <t>1,731,250</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -1327,17 +1327,17 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>7,408,484</t>
+          <t>42,156,224</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -1349,17 +1349,17 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>1,731,250</t>
+          <t>7,408,484</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
